--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27350.65</v>
+        <v>27315.84</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26283.61</v>
+        <v>26370.06</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>13924.72</v>
+        <v>13874.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8845.02</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6322.95</v>
+        <v>6317.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13237.85</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7966.42</v>
+        <v>7950.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>51300.07</v>
+        <v>51029.08</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12586.07</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23228.27</v>
+        <v>23439.55</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>16458.26</v>
+        <v>16604.85</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6397.29</v>
+        <v>6362.45</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8568.48</v>
+        <v>8602.26</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8880.01</v>
+        <v>8887.66</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21477.51</v>
+        <v>21384.99</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7505.32</v>
+        <v>7605.24</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>59736.47</v>
+        <v>60531.72</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11381.53</v>
+        <v>11508.82</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>29430.3</v>
+        <v>29653.22</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7319.35</v>
+        <v>7300.87</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46477.6</v>
+        <v>46625.52</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13412.32</v>
+        <v>13483.64</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9753.360000000001</v>
+        <v>9867.77</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10756.52</v>
+        <v>10608.72</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7287.65</v>
+        <v>7320.75</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6593.48</v>
+        <v>6495.8</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6515.12</v>
+        <v>6540.55</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5701.41</v>
+        <v>5758.75</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>36632.76</v>
+        <v>37001.19</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15787.28</v>
+        <v>15534.15</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8155.24</v>
+        <v>8110.03</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1232565-400-CM25</t>
+          <t>624-251-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27315.84</v>
+        <v>22757.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2997-232-CM25</t>
+          <t>1232565-400-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26370.06</v>
+        <v>27315.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3265-2149-CM25</t>
+          <t>2997-232-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>13874.79</v>
+        <v>26370.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1232565-498-CM25</t>
+          <t>3265-2149-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8837.91</v>
+        <v>13874.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>707418-229-CM25</t>
+          <t>1232565-498-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,17 +778,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6317.86</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1495203-6-CM25</t>
+          <t>707418-229-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13328.97</v>
+        <v>6317.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1004823-4-CM26</t>
+          <t>1495203-6-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7950.73</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1232565-20-CM26</t>
+          <t>1004823-4-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>51029.08</v>
+        <v>7950.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2446-154-CM26</t>
+          <t>1232565-20-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12533</v>
+        <v>51029.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3714-24-CM26</t>
+          <t>2446-154-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23439.55</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2450-122-CM26</t>
+          <t>3714-24-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>16604.85</v>
+        <v>23439.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3714-33-CM26</t>
+          <t>2450-122-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6362.45</v>
+        <v>16604.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3712-183-CM26</t>
+          <t>3714-33-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8602.26</v>
+        <v>6362.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1232565-47-CM26</t>
+          <t>3712-183-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8887.66</v>
+        <v>8602.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714-83-CM26</t>
+          <t>1232565-47-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21384.99</v>
+        <v>8887.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3712-296-CM26</t>
+          <t>3714-83-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7605.24</v>
+        <v>21384.99</v>
       </c>
     </row>
     <row r="18">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1284073-21-CM26</t>
+          <t>3712-296-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11508.82</v>
+        <v>7605.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2448-180-CM26</t>
+          <t>1284073-21-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>29653.22</v>
+        <v>11508.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1471-38-CM26</t>
+          <t>2448-180-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7300.87</v>
+        <v>29653.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2446-603-CM26</t>
+          <t>1471-38-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46625.52</v>
+        <v>7300.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1471-45-CM26</t>
+          <t>2446-603-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13483.64</v>
+        <v>46625.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1232565-129-CM26</t>
+          <t>1471-45-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9867.77</v>
+        <v>13483.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1461054-227-CM26</t>
+          <t>1232565-129-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10608.72</v>
+        <v>9867.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1232565-159-CM26</t>
+          <t>1461054-227-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7320.75</v>
+        <v>10608.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1232565-182-CM26</t>
+          <t>1232565-159-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6495.8</v>
+        <v>7320.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1698-174-CM26</t>
+          <t>1232565-182-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6540.55</v>
+        <v>6495.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1471-59-CM26</t>
+          <t>1698-174-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5758.75</v>
+        <v>6540.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1430710-484-CM26</t>
+          <t>1471-59-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>37001.19</v>
+        <v>5758.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3712-530-CM26</t>
+          <t>1430710-484-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15534.15</v>
+        <v>37001.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3714-208-CM26</t>
+          <t>3712-530-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2399,6 +2399,67 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
+        <v>15534.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3714-208-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>8110.03</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>624-251-CM25</t>
+          <t>1232565-6-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>22757.63</v>
+        <v>41541.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1232565-400-CM25</t>
+          <t>2450-147-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>27315.84</v>
+        <v>12935.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2997-232-CM25</t>
+          <t>627786-28-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26370.06</v>
+        <v>7249.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3265-2149-CM25</t>
+          <t>1004823-26-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13874.79</v>
+        <v>8238.969999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1232565-498-CM25</t>
+          <t>1232565-55-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8837.91</v>
+        <v>8752.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>707418-229-CM25</t>
+          <t>1698-170-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6317.86</v>
+        <v>5858.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1495203-6-CM25</t>
+          <t>1698-202-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13328.97</v>
+        <v>7018.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1004823-4-CM26</t>
+          <t>1232565-185-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7950.73</v>
+        <v>40144.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1232565-20-CM26</t>
+          <t>2448-694-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>51029.08</v>
+        <v>23811.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2446-154-CM26</t>
+          <t>1232565-283-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>12533</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3714-24-CM26</t>
+          <t>624-251-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,28 +1179,28 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23439.55</v>
+        <v>22757.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2450-122-CM26</t>
+          <t>4295-33-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16604.85</v>
+        <v>49737.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714-33-CM26</t>
+          <t>2450-761-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6362.45</v>
+        <v>18014.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3712-183-CM26</t>
+          <t>3276-33-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8602.26</v>
+        <v>8774.059999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1232565-47-CM26</t>
+          <t>1232565-400-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8887.66</v>
+        <v>27315.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3714-83-CM26</t>
+          <t>2997-232-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21384.99</v>
+        <v>26370.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5416-296-CM26</t>
+          <t>3265-2149-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>60531.72</v>
+        <v>13874.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3712-296-CM26</t>
+          <t>707418-229-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7605.24</v>
+        <v>6317.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1284073-21-CM26</t>
+          <t>1232565-498-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11508.82</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2448-180-CM26</t>
+          <t>1495203-6-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>29653.22</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1471-38-CM26</t>
+          <t>1004823-4-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7300.87</v>
+        <v>7950.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2446-603-CM26</t>
+          <t>1232565-20-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>46625.52</v>
+        <v>51029.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1471-45-CM26</t>
+          <t>2446-154-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13483.64</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1232565-129-CM26</t>
+          <t>3714-24-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9867.77</v>
+        <v>23439.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1461054-227-CM26</t>
+          <t>2450-122-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10608.72</v>
+        <v>16604.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1232565-159-CM26</t>
+          <t>3714-33-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7320.75</v>
+        <v>6362.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1232565-182-CM26</t>
+          <t>3712-183-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6495.8</v>
+        <v>8602.26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1698-174-CM26</t>
+          <t>1232565-47-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6540.55</v>
+        <v>8887.66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1471-59-CM26</t>
+          <t>3714-83-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5758.75</v>
+        <v>21384.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1430710-484-CM26</t>
+          <t>5416-296-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>37001.19</v>
+        <v>60531.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3712-530-CM26</t>
+          <t>3712-296-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15534.15</v>
+        <v>7605.24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3714-208-CM26</t>
+          <t>1284073-21-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2460,1166 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>11508.82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2448-180-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>29653.22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1471-38-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>7300.87</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2446-603-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>46625.52</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1471-45-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>13483.64</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1232565-129-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>9867.77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1461054-227-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>10608.72</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1232565-159-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>7320.75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1232565-182-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>6495.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1698-174-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>6540.55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1471-59-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>5758.75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1430710-484-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>37001.19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3712-530-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>15534.15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3714-208-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>8110.03</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3714-218-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>15549.88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2288-667-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>90497.82000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1232565-213-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>6400.97</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1232565-216-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>7106.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5416-802-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>9177.83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2145-711-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>15895.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3620,6 +3620,189 @@
       </c>
       <c r="M52" s="2" t="n">
         <v>15895.55</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5416-961-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>5596.18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1461054-352-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>73103.75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1232565-314-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>5654.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2167,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2423,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2488,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2553,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2618,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2996,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3061,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3187,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3252,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3317,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3382,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3447,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3512,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3577,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3642,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3707,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3833,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3959,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -3805,7 +3805,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/coquimbo.xlsx
@@ -2907,7 +2907,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
